--- a/templates/invigilation-template.xlsx
+++ b/templates/invigilation-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4378561C-8FB2-4A74-B495-60F7E44E24DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF02F03F-3DD3-4FEF-B19A-683AFA70A135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2D53BEDC-658E-4916-BAED-16A4B4875AEA}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="30">
   <si>
     <t>日  期</t>
   </si>
@@ -132,6 +132,21 @@
   </si>
   <si>
     <t>16:00</t>
+  </si>
+  <si>
+    <t>自習</t>
+  </si>
+  <si>
+    <t>自習</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>節次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日  期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -255,7 +270,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -264,30 +279,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
       <top style="thick">
         <color auto="1"/>
       </top>
@@ -351,19 +344,6 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
@@ -447,8 +427,106 @@
       </left>
       <right/>
       <top/>
-      <bottom style="thick">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -456,48 +534,39 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thick">
-        <color rgb="FF000000"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -506,91 +575,106 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -823,75 +907,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="2" customFormat="1" ht="43.5" customHeight="1" thickTop="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="31"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="40"/>
       <c r="Y1" s="1"/>
     </row>
     <row r="2" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="32" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="15" t="s">
-        <v>0</v>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="14" t="s">
+        <v>29</v>
       </c>
-      <c r="N2" s="32" t="s">
+      <c r="N2" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="32" t="s">
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="35"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="42"/>
       <c r="Y2" s="3"/>
     </row>
     <row r="3" spans="1:25" ht="27.75" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="41" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="15">
@@ -927,8 +1011,8 @@
       <c r="L3" s="16">
         <v>4</v>
       </c>
-      <c r="M3" s="15" t="s">
-        <v>1</v>
+      <c r="M3" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="N3" s="15">
         <v>1</v>
@@ -960,1333 +1044,1411 @@
       <c r="W3" s="18">
         <v>3</v>
       </c>
-      <c r="X3" s="19">
+      <c r="X3" s="43">
         <v>4</v>
       </c>
       <c r="Y3" s="4"/>
     </row>
     <row r="4" spans="1:25" ht="27.75" customHeight="1">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="15"/>
+      <c r="B4" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="C4" s="16"/>
-      <c r="D4" s="15"/>
+      <c r="D4" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="E4" s="17"/>
-      <c r="F4" s="15"/>
+      <c r="F4" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="G4" s="16"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
+      <c r="H4" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="J4" s="16"/>
-      <c r="K4" s="15"/>
+      <c r="K4" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="L4" s="17"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
+      <c r="M4" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="N4" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="O4" s="16"/>
-      <c r="P4" s="15"/>
+      <c r="P4" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="Q4" s="17"/>
-      <c r="R4" s="15"/>
+      <c r="R4" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="S4" s="16"/>
-      <c r="T4" s="15"/>
-      <c r="U4" s="15"/>
+      <c r="T4" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="U4" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="V4" s="16"/>
-      <c r="W4" s="18"/>
-      <c r="X4" s="20"/>
+      <c r="W4" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="X4" s="44"/>
       <c r="Y4" s="4"/>
     </row>
     <row r="5" spans="1:25" ht="27.75" customHeight="1">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="15"/>
+      <c r="B5" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="C5" s="16"/>
-      <c r="D5" s="15"/>
+      <c r="D5" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="E5" s="17"/>
-      <c r="F5" s="15"/>
+      <c r="F5" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="G5" s="16"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="H5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="J5" s="17"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="L5" s="17"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
+      <c r="M5" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="O5" s="16"/>
-      <c r="P5" s="15"/>
+      <c r="P5" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="Q5" s="17"/>
-      <c r="R5" s="15"/>
+      <c r="R5" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="S5" s="16"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
+      <c r="T5" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="U5" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="V5" s="17"/>
-      <c r="W5" s="18"/>
-      <c r="X5" s="20"/>
+      <c r="W5" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="X5" s="44"/>
       <c r="Y5" s="4"/>
     </row>
     <row r="6" spans="1:25" ht="27.75" customHeight="1">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="15"/>
+      <c r="B6" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="C6" s="16"/>
-      <c r="D6" s="15"/>
+      <c r="D6" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="E6" s="17"/>
-      <c r="F6" s="15"/>
+      <c r="F6" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="G6" s="16"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
+      <c r="H6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="J6" s="17"/>
-      <c r="K6" s="15"/>
+      <c r="K6" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="L6" s="17"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
+      <c r="M6" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="O6" s="16"/>
-      <c r="P6" s="15"/>
+      <c r="P6" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="Q6" s="17"/>
-      <c r="R6" s="15"/>
+      <c r="R6" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="S6" s="16"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
+      <c r="T6" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="U6" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="V6" s="17"/>
-      <c r="W6" s="18"/>
-      <c r="X6" s="20"/>
+      <c r="W6" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="X6" s="44"/>
       <c r="Y6" s="4"/>
     </row>
     <row r="7" spans="1:25" ht="33" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="F7" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="39" t="s">
+      <c r="H7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="36" t="s">
+      <c r="I7" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="40" t="s">
+      <c r="K7" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="41" t="s">
+      <c r="L7" s="29" t="s">
         <v>15</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="36" t="s">
+      <c r="N7" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="37" t="s">
+      <c r="O7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="P7" s="36" t="s">
+      <c r="P7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="Q7" s="38" t="s">
+      <c r="Q7" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R7" s="39" t="s">
+      <c r="R7" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="S7" s="37" t="s">
+      <c r="S7" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="T7" s="39" t="s">
+      <c r="T7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="U7" s="36" t="s">
+      <c r="U7" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="V7" s="37" t="s">
+      <c r="V7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="W7" s="40" t="s">
+      <c r="W7" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="X7" s="41" t="s">
+      <c r="X7" s="45" t="s">
         <v>15</v>
       </c>
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="1:25" ht="30.75" customHeight="1">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="G8" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="39" t="s">
+      <c r="H8" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="39" t="s">
+      <c r="I8" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="37" t="s">
+      <c r="J8" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="K8" s="42" t="s">
+      <c r="K8" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="43" t="s">
+      <c r="L8" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="21" t="s">
+      <c r="M8" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="N8" s="39" t="s">
+      <c r="N8" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="O8" s="37" t="s">
+      <c r="O8" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="39" t="s">
+      <c r="P8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="37" t="s">
+      <c r="Q8" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="39" t="s">
+      <c r="R8" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="S8" s="37" t="s">
+      <c r="S8" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="T8" s="39" t="s">
+      <c r="T8" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="U8" s="39" t="s">
+      <c r="U8" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="V8" s="37" t="s">
+      <c r="V8" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="W8" s="42" t="s">
+      <c r="W8" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="X8" s="43" t="s">
+      <c r="X8" s="46" t="s">
         <v>22</v>
       </c>
       <c r="Y8" s="5"/>
     </row>
     <row r="9" spans="1:25" ht="27.65" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23"/>
+      <c r="A9" s="47"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="25"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="23"/>
       <c r="M9" s="6"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="23"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="21"/>
       <c r="P9" s="7"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="24"/>
-      <c r="X9" s="25"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="48"/>
       <c r="Y9" s="8"/>
     </row>
     <row r="10" spans="1:25" ht="30.65" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="23"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="21"/>
       <c r="D10" s="7"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="25"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="23"/>
       <c r="M10" s="6"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="23"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="21"/>
       <c r="P10" s="7"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="24"/>
-      <c r="X10" s="25"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="21"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="48"/>
       <c r="Y10" s="8"/>
     </row>
     <row r="11" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="23"/>
+      <c r="A11" s="47"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="21"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="25"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="23"/>
       <c r="M11" s="6"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="23"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="21"/>
       <c r="P11" s="7"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="24"/>
-      <c r="X11" s="25"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="21"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="48"/>
       <c r="Y11" s="8"/>
     </row>
     <row r="12" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="23"/>
+      <c r="A12" s="47"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="21"/>
       <c r="D12" s="7"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="25"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="23"/>
       <c r="M12" s="6"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="23"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="21"/>
       <c r="P12" s="7"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="24"/>
-      <c r="X12" s="25"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="48"/>
       <c r="Y12" s="8"/>
     </row>
     <row r="13" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="23"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="21"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="25"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="23"/>
       <c r="M13" s="6"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="23"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="21"/>
       <c r="P13" s="7"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="24"/>
-      <c r="X13" s="25"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="48"/>
       <c r="Y13" s="8"/>
     </row>
     <row r="14" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
+      <c r="A14" s="47"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="21"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="25"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="23"/>
       <c r="M14" s="6"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="23"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="21"/>
       <c r="P14" s="7"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="25"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="48"/>
       <c r="Y14" s="8"/>
     </row>
     <row r="15" spans="1:25" ht="30.75" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23"/>
+      <c r="A15" s="47"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="21"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="25"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="23"/>
       <c r="M15" s="6"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="23"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="21"/>
       <c r="P15" s="7"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="23"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="22"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="25"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="21"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="48"/>
       <c r="Y15" s="8"/>
     </row>
     <row r="16" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="23"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="21"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="25"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="23"/>
       <c r="M16" s="6"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="23"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
       <c r="P16" s="7"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="22"/>
-      <c r="U16" s="22"/>
-      <c r="V16" s="23"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="25"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="21"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="48"/>
       <c r="Y16" s="8"/>
     </row>
     <row r="17" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="25"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="23"/>
       <c r="M17" s="6"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="23"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="21"/>
       <c r="P17" s="7"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="22"/>
-      <c r="U17" s="22"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="25"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="21"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="48"/>
       <c r="Y17" s="8"/>
     </row>
     <row r="18" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="23"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
       <c r="D18" s="7"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="25"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="23"/>
       <c r="M18" s="6"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="23"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="21"/>
       <c r="P18" s="7"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="23"/>
-      <c r="T18" s="22"/>
-      <c r="U18" s="22"/>
-      <c r="V18" s="23"/>
-      <c r="W18" s="24"/>
-      <c r="X18" s="25"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="21"/>
+      <c r="W18" s="22"/>
+      <c r="X18" s="48"/>
       <c r="Y18" s="8"/>
     </row>
     <row r="19" spans="1:25" ht="27.75" customHeight="1">
-      <c r="A19" s="6"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="25"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="23"/>
       <c r="M19" s="6"/>
-      <c r="N19" s="22"/>
-      <c r="O19" s="23"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="21"/>
       <c r="P19" s="7"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="22"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="22"/>
-      <c r="U19" s="22"/>
-      <c r="V19" s="23"/>
-      <c r="W19" s="24"/>
-      <c r="X19" s="25"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="22"/>
+      <c r="X19" s="48"/>
       <c r="Y19" s="8"/>
     </row>
     <row r="20" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="23"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="25"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="23"/>
       <c r="M20" s="6"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="23"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="21"/>
       <c r="P20" s="7"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="22"/>
-      <c r="S20" s="23"/>
-      <c r="T20" s="22"/>
-      <c r="U20" s="22"/>
-      <c r="V20" s="23"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="25"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="21"/>
+      <c r="W20" s="22"/>
+      <c r="X20" s="48"/>
       <c r="Y20" s="8"/>
     </row>
     <row r="21" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="23"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="21"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="25"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="23"/>
       <c r="M21" s="6"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="23"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="21"/>
       <c r="P21" s="7"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="22"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="22"/>
-      <c r="U21" s="22"/>
-      <c r="V21" s="23"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="25"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="21"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="21"/>
+      <c r="W21" s="22"/>
+      <c r="X21" s="48"/>
       <c r="Y21" s="8"/>
     </row>
     <row r="22" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="23"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="21"/>
       <c r="D22" s="7"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="25"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="23"/>
       <c r="M22" s="6"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="23"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="21"/>
       <c r="P22" s="7"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="22"/>
-      <c r="S22" s="23"/>
-      <c r="T22" s="22"/>
-      <c r="U22" s="22"/>
-      <c r="V22" s="23"/>
-      <c r="W22" s="24"/>
-      <c r="X22" s="25"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="21"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="21"/>
+      <c r="W22" s="22"/>
+      <c r="X22" s="48"/>
       <c r="Y22" s="8"/>
     </row>
     <row r="23" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="23"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="21"/>
       <c r="D23" s="7"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="25"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="23"/>
       <c r="M23" s="6"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="23"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="21"/>
       <c r="P23" s="7"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="22"/>
-      <c r="S23" s="23"/>
-      <c r="T23" s="22"/>
-      <c r="U23" s="22"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="24"/>
-      <c r="X23" s="25"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="21"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="21"/>
+      <c r="W23" s="22"/>
+      <c r="X23" s="48"/>
       <c r="Y23" s="8"/>
     </row>
     <row r="24" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23"/>
+      <c r="A24" s="47"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="21"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="25"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="23"/>
       <c r="M24" s="6"/>
-      <c r="N24" s="22"/>
-      <c r="O24" s="23"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="21"/>
       <c r="P24" s="7"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="22"/>
-      <c r="S24" s="23"/>
-      <c r="T24" s="22"/>
-      <c r="U24" s="22"/>
-      <c r="V24" s="23"/>
-      <c r="W24" s="24"/>
-      <c r="X24" s="25"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="21"/>
+      <c r="W24" s="22"/>
+      <c r="X24" s="48"/>
       <c r="Y24" s="8"/>
     </row>
     <row r="25" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23"/>
+      <c r="A25" s="47"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="21"/>
       <c r="D25" s="7"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="25"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="23"/>
       <c r="M25" s="6"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="23"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="21"/>
       <c r="P25" s="7"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="22"/>
-      <c r="S25" s="23"/>
-      <c r="T25" s="22"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="23"/>
-      <c r="W25" s="24"/>
-      <c r="X25" s="25"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="21"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="21"/>
+      <c r="W25" s="22"/>
+      <c r="X25" s="48"/>
       <c r="Y25" s="8"/>
     </row>
     <row r="26" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A26" s="6"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="23"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="21"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="25"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="23"/>
       <c r="M26" s="6"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="23"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="21"/>
       <c r="P26" s="7"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="22"/>
-      <c r="S26" s="23"/>
-      <c r="T26" s="22"/>
-      <c r="U26" s="22"/>
-      <c r="V26" s="23"/>
-      <c r="W26" s="24"/>
-      <c r="X26" s="25"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="21"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="21"/>
+      <c r="W26" s="22"/>
+      <c r="X26" s="48"/>
       <c r="Y26" s="8"/>
     </row>
     <row r="27" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A27" s="6"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="23"/>
+      <c r="A27" s="47"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="21"/>
       <c r="D27" s="7"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="25"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="23"/>
       <c r="M27" s="6"/>
-      <c r="N27" s="22"/>
-      <c r="O27" s="23"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="21"/>
       <c r="P27" s="7"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="22"/>
-      <c r="S27" s="23"/>
-      <c r="T27" s="22"/>
-      <c r="U27" s="22"/>
-      <c r="V27" s="23"/>
-      <c r="W27" s="24"/>
-      <c r="X27" s="25"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="21"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="21"/>
+      <c r="W27" s="22"/>
+      <c r="X27" s="48"/>
       <c r="Y27" s="8"/>
     </row>
     <row r="28" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A28" s="6"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="23"/>
+      <c r="A28" s="47"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="21"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="25"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="23"/>
       <c r="M28" s="6"/>
-      <c r="N28" s="22"/>
-      <c r="O28" s="23"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="21"/>
       <c r="P28" s="7"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="22"/>
-      <c r="S28" s="23"/>
-      <c r="T28" s="22"/>
-      <c r="U28" s="22"/>
-      <c r="V28" s="23"/>
-      <c r="W28" s="24"/>
-      <c r="X28" s="25"/>
+      <c r="Q28" s="21"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="21"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="21"/>
+      <c r="W28" s="22"/>
+      <c r="X28" s="48"/>
       <c r="Y28" s="8"/>
     </row>
     <row r="29" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A29" s="6"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="23"/>
+      <c r="A29" s="47"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="21"/>
       <c r="D29" s="7"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="25"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="23"/>
       <c r="M29" s="6"/>
-      <c r="N29" s="22"/>
-      <c r="O29" s="23"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="21"/>
       <c r="P29" s="7"/>
-      <c r="Q29" s="23"/>
-      <c r="R29" s="22"/>
-      <c r="S29" s="23"/>
-      <c r="T29" s="22"/>
-      <c r="U29" s="22"/>
-      <c r="V29" s="23"/>
-      <c r="W29" s="24"/>
-      <c r="X29" s="25"/>
+      <c r="Q29" s="21"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="21"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="21"/>
+      <c r="W29" s="22"/>
+      <c r="X29" s="48"/>
       <c r="Y29" s="8"/>
     </row>
     <row r="30" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A30" s="6"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="23"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="21"/>
       <c r="D30" s="7"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="25"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="23"/>
       <c r="M30" s="6"/>
-      <c r="N30" s="22"/>
-      <c r="O30" s="23"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="21"/>
       <c r="P30" s="7"/>
-      <c r="Q30" s="23"/>
-      <c r="R30" s="22"/>
-      <c r="S30" s="23"/>
-      <c r="T30" s="22"/>
-      <c r="U30" s="22"/>
-      <c r="V30" s="23"/>
-      <c r="W30" s="24"/>
-      <c r="X30" s="25"/>
+      <c r="Q30" s="21"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="21"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="21"/>
+      <c r="W30" s="22"/>
+      <c r="X30" s="48"/>
       <c r="Y30" s="8"/>
     </row>
     <row r="31" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="23"/>
+      <c r="A31" s="47"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="21"/>
       <c r="D31" s="7"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="25"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="23"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="22"/>
-      <c r="O31" s="23"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="21"/>
       <c r="P31" s="7"/>
-      <c r="Q31" s="23"/>
-      <c r="R31" s="22"/>
-      <c r="S31" s="23"/>
-      <c r="T31" s="22"/>
-      <c r="U31" s="22"/>
-      <c r="V31" s="23"/>
-      <c r="W31" s="24"/>
-      <c r="X31" s="25"/>
+      <c r="Q31" s="21"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="21"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="21"/>
+      <c r="W31" s="22"/>
+      <c r="X31" s="48"/>
       <c r="Y31" s="8"/>
     </row>
     <row r="32" spans="1:25" ht="30" customHeight="1">
-      <c r="A32" s="6"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="23"/>
+      <c r="A32" s="47"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="21"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="25"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="23"/>
       <c r="M32" s="6"/>
-      <c r="N32" s="22"/>
-      <c r="O32" s="23"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="21"/>
       <c r="P32" s="7"/>
-      <c r="Q32" s="23"/>
-      <c r="R32" s="22"/>
-      <c r="S32" s="23"/>
-      <c r="T32" s="22"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="23"/>
-      <c r="W32" s="24"/>
-      <c r="X32" s="25"/>
+      <c r="Q32" s="21"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="21"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="20"/>
+      <c r="V32" s="21"/>
+      <c r="W32" s="22"/>
+      <c r="X32" s="48"/>
       <c r="Y32" s="8"/>
     </row>
     <row r="33" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A33" s="6"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="23"/>
+      <c r="A33" s="47"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="21"/>
       <c r="D33" s="7"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="25"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="23"/>
       <c r="M33" s="6"/>
-      <c r="N33" s="22"/>
-      <c r="O33" s="23"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="21"/>
       <c r="P33" s="7"/>
-      <c r="Q33" s="23"/>
-      <c r="R33" s="22"/>
-      <c r="S33" s="23"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="22"/>
-      <c r="V33" s="23"/>
-      <c r="W33" s="24"/>
-      <c r="X33" s="25"/>
+      <c r="Q33" s="21"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="21"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="20"/>
+      <c r="V33" s="21"/>
+      <c r="W33" s="22"/>
+      <c r="X33" s="48"/>
       <c r="Y33" s="8"/>
     </row>
     <row r="34" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A34" s="6"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="23"/>
+      <c r="A34" s="47"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="21"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="25"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="21"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="23"/>
       <c r="M34" s="6"/>
-      <c r="N34" s="22"/>
-      <c r="O34" s="23"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="21"/>
       <c r="P34" s="7"/>
-      <c r="Q34" s="23"/>
-      <c r="R34" s="22"/>
-      <c r="S34" s="23"/>
-      <c r="T34" s="22"/>
-      <c r="U34" s="22"/>
-      <c r="V34" s="23"/>
-      <c r="W34" s="24"/>
-      <c r="X34" s="25"/>
+      <c r="Q34" s="21"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="21"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="21"/>
+      <c r="W34" s="22"/>
+      <c r="X34" s="48"/>
       <c r="Y34" s="8"/>
     </row>
     <row r="35" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="23"/>
+      <c r="A35" s="47"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="21"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="25"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="23"/>
       <c r="M35" s="6"/>
-      <c r="N35" s="22"/>
-      <c r="O35" s="23"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="21"/>
       <c r="P35" s="7"/>
-      <c r="Q35" s="23"/>
-      <c r="R35" s="22"/>
-      <c r="S35" s="23"/>
-      <c r="T35" s="22"/>
-      <c r="U35" s="22"/>
-      <c r="V35" s="23"/>
-      <c r="W35" s="24"/>
-      <c r="X35" s="25"/>
+      <c r="Q35" s="21"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="21"/>
+      <c r="T35" s="20"/>
+      <c r="U35" s="20"/>
+      <c r="V35" s="21"/>
+      <c r="W35" s="22"/>
+      <c r="X35" s="48"/>
       <c r="Y35" s="8"/>
     </row>
     <row r="36" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A36" s="6"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="23"/>
+      <c r="A36" s="47"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="21"/>
       <c r="D36" s="7"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="25"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="23"/>
       <c r="M36" s="6"/>
-      <c r="N36" s="22"/>
-      <c r="O36" s="23"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="21"/>
       <c r="P36" s="7"/>
-      <c r="Q36" s="23"/>
-      <c r="R36" s="22"/>
-      <c r="S36" s="23"/>
-      <c r="T36" s="22"/>
-      <c r="U36" s="22"/>
-      <c r="V36" s="23"/>
-      <c r="W36" s="24"/>
-      <c r="X36" s="25"/>
+      <c r="Q36" s="21"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="21"/>
+      <c r="T36" s="20"/>
+      <c r="U36" s="20"/>
+      <c r="V36" s="21"/>
+      <c r="W36" s="22"/>
+      <c r="X36" s="48"/>
       <c r="Y36" s="8"/>
     </row>
     <row r="37" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A37" s="6"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="23"/>
+      <c r="A37" s="47"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="21"/>
       <c r="D37" s="7"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="23"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="25"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="23"/>
       <c r="M37" s="6"/>
-      <c r="N37" s="22"/>
-      <c r="O37" s="23"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="21"/>
       <c r="P37" s="7"/>
-      <c r="Q37" s="23"/>
-      <c r="R37" s="22"/>
-      <c r="S37" s="23"/>
-      <c r="T37" s="22"/>
-      <c r="U37" s="22"/>
-      <c r="V37" s="23"/>
-      <c r="W37" s="24"/>
-      <c r="X37" s="25"/>
+      <c r="Q37" s="21"/>
+      <c r="R37" s="20"/>
+      <c r="S37" s="21"/>
+      <c r="T37" s="20"/>
+      <c r="U37" s="20"/>
+      <c r="V37" s="21"/>
+      <c r="W37" s="22"/>
+      <c r="X37" s="48"/>
       <c r="Y37" s="8"/>
     </row>
     <row r="38" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A38" s="6"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="23"/>
+      <c r="A38" s="47"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="21"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="23"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="25"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="23"/>
       <c r="M38" s="6"/>
-      <c r="N38" s="22"/>
-      <c r="O38" s="23"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="21"/>
       <c r="P38" s="7"/>
-      <c r="Q38" s="23"/>
-      <c r="R38" s="22"/>
-      <c r="S38" s="23"/>
-      <c r="T38" s="22"/>
-      <c r="U38" s="22"/>
-      <c r="V38" s="23"/>
-      <c r="W38" s="24"/>
-      <c r="X38" s="25"/>
+      <c r="Q38" s="21"/>
+      <c r="R38" s="20"/>
+      <c r="S38" s="21"/>
+      <c r="T38" s="20"/>
+      <c r="U38" s="20"/>
+      <c r="V38" s="21"/>
+      <c r="W38" s="22"/>
+      <c r="X38" s="48"/>
       <c r="Y38" s="8"/>
     </row>
     <row r="39" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="23"/>
+      <c r="A39" s="47"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="21"/>
       <c r="D39" s="7"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="23"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="25"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="23"/>
       <c r="M39" s="6"/>
-      <c r="N39" s="22"/>
-      <c r="O39" s="23"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="21"/>
       <c r="P39" s="7"/>
-      <c r="Q39" s="23"/>
-      <c r="R39" s="22"/>
-      <c r="S39" s="23"/>
-      <c r="T39" s="22"/>
-      <c r="U39" s="22"/>
-      <c r="V39" s="23"/>
-      <c r="W39" s="24"/>
-      <c r="X39" s="25"/>
+      <c r="Q39" s="21"/>
+      <c r="R39" s="20"/>
+      <c r="S39" s="21"/>
+      <c r="T39" s="20"/>
+      <c r="U39" s="20"/>
+      <c r="V39" s="21"/>
+      <c r="W39" s="22"/>
+      <c r="X39" s="48"/>
       <c r="Y39" s="8"/>
     </row>
     <row r="40" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A40" s="6"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="23"/>
+      <c r="A40" s="47"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="21"/>
       <c r="D40" s="7"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="25"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="23"/>
       <c r="M40" s="6"/>
-      <c r="N40" s="22"/>
-      <c r="O40" s="23"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="21"/>
       <c r="P40" s="7"/>
-      <c r="Q40" s="23"/>
-      <c r="R40" s="22"/>
-      <c r="S40" s="23"/>
-      <c r="T40" s="22"/>
-      <c r="U40" s="22"/>
-      <c r="V40" s="23"/>
-      <c r="W40" s="24"/>
-      <c r="X40" s="25"/>
+      <c r="Q40" s="21"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="21"/>
+      <c r="T40" s="20"/>
+      <c r="U40" s="20"/>
+      <c r="V40" s="21"/>
+      <c r="W40" s="22"/>
+      <c r="X40" s="48"/>
       <c r="Y40" s="8"/>
     </row>
     <row r="41" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A41" s="6"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="23"/>
+      <c r="A41" s="47"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="21"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="23"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="25"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="23"/>
       <c r="M41" s="6"/>
-      <c r="N41" s="22"/>
-      <c r="O41" s="23"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="21"/>
       <c r="P41" s="7"/>
-      <c r="Q41" s="23"/>
-      <c r="R41" s="22"/>
-      <c r="S41" s="23"/>
-      <c r="T41" s="22"/>
-      <c r="U41" s="22"/>
-      <c r="V41" s="23"/>
-      <c r="W41" s="24"/>
-      <c r="X41" s="25"/>
+      <c r="Q41" s="21"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="21"/>
+      <c r="T41" s="20"/>
+      <c r="U41" s="20"/>
+      <c r="V41" s="21"/>
+      <c r="W41" s="22"/>
+      <c r="X41" s="48"/>
       <c r="Y41" s="8"/>
     </row>
     <row r="42" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A42" s="6"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="23"/>
+      <c r="A42" s="47"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="21"/>
       <c r="D42" s="7"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="23"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="25"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="23"/>
       <c r="M42" s="6"/>
-      <c r="N42" s="22"/>
-      <c r="O42" s="23"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="21"/>
       <c r="P42" s="7"/>
-      <c r="Q42" s="23"/>
-      <c r="R42" s="22"/>
-      <c r="S42" s="23"/>
-      <c r="T42" s="22"/>
-      <c r="U42" s="22"/>
-      <c r="V42" s="23"/>
-      <c r="W42" s="24"/>
-      <c r="X42" s="25"/>
+      <c r="Q42" s="21"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="21"/>
+      <c r="T42" s="20"/>
+      <c r="U42" s="20"/>
+      <c r="V42" s="21"/>
+      <c r="W42" s="22"/>
+      <c r="X42" s="48"/>
       <c r="Y42" s="8"/>
     </row>
     <row r="43" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A43" s="6"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="23"/>
+      <c r="A43" s="47"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="21"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="23"/>
-      <c r="K43" s="24"/>
-      <c r="L43" s="25"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="23"/>
       <c r="M43" s="6"/>
-      <c r="N43" s="22"/>
-      <c r="O43" s="23"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="21"/>
       <c r="P43" s="7"/>
-      <c r="Q43" s="23"/>
-      <c r="R43" s="22"/>
-      <c r="S43" s="23"/>
-      <c r="T43" s="22"/>
-      <c r="U43" s="22"/>
-      <c r="V43" s="23"/>
-      <c r="W43" s="24"/>
-      <c r="X43" s="25"/>
+      <c r="Q43" s="21"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="21"/>
+      <c r="T43" s="20"/>
+      <c r="U43" s="20"/>
+      <c r="V43" s="21"/>
+      <c r="W43" s="22"/>
+      <c r="X43" s="48"/>
       <c r="Y43" s="8"/>
     </row>
     <row r="44" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A44" s="6"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="23"/>
+      <c r="A44" s="47"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="21"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="22"/>
-      <c r="I44" s="22"/>
-      <c r="J44" s="23"/>
-      <c r="K44" s="24"/>
-      <c r="L44" s="25"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="21"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="23"/>
       <c r="M44" s="6"/>
-      <c r="N44" s="22"/>
-      <c r="O44" s="23"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="21"/>
       <c r="P44" s="7"/>
-      <c r="Q44" s="23"/>
-      <c r="R44" s="22"/>
-      <c r="S44" s="23"/>
-      <c r="T44" s="22"/>
-      <c r="U44" s="22"/>
-      <c r="V44" s="23"/>
-      <c r="W44" s="24"/>
-      <c r="X44" s="25"/>
+      <c r="Q44" s="21"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="21"/>
+      <c r="T44" s="20"/>
+      <c r="U44" s="20"/>
+      <c r="V44" s="21"/>
+      <c r="W44" s="22"/>
+      <c r="X44" s="48"/>
       <c r="Y44" s="8"/>
     </row>
     <row r="45" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A45" s="6"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="23"/>
+      <c r="A45" s="47"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="21"/>
       <c r="D45" s="7"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="23"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="23"/>
-      <c r="K45" s="24"/>
-      <c r="L45" s="25"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="23"/>
       <c r="M45" s="6"/>
-      <c r="N45" s="22"/>
-      <c r="O45" s="23"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="21"/>
       <c r="P45" s="7"/>
-      <c r="Q45" s="23"/>
-      <c r="R45" s="22"/>
-      <c r="S45" s="23"/>
-      <c r="T45" s="22"/>
-      <c r="U45" s="22"/>
-      <c r="V45" s="23"/>
-      <c r="W45" s="24"/>
-      <c r="X45" s="25"/>
+      <c r="Q45" s="21"/>
+      <c r="R45" s="20"/>
+      <c r="S45" s="21"/>
+      <c r="T45" s="20"/>
+      <c r="U45" s="20"/>
+      <c r="V45" s="21"/>
+      <c r="W45" s="22"/>
+      <c r="X45" s="48"/>
       <c r="Y45" s="8"/>
     </row>
     <row r="46" spans="1:25" ht="28.5" customHeight="1" thickBot="1">
-      <c r="A46" s="6"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="23"/>
+      <c r="A46" s="47"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="21"/>
       <c r="D46" s="7"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="23"/>
-      <c r="K46" s="24"/>
-      <c r="L46" s="25"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="21"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="23"/>
       <c r="M46" s="6"/>
-      <c r="N46" s="22"/>
-      <c r="O46" s="23"/>
+      <c r="N46" s="20"/>
+      <c r="O46" s="21"/>
       <c r="P46" s="7"/>
-      <c r="Q46" s="23"/>
-      <c r="R46" s="22"/>
-      <c r="S46" s="23"/>
-      <c r="T46" s="22"/>
-      <c r="U46" s="22"/>
-      <c r="V46" s="23"/>
-      <c r="W46" s="24"/>
-      <c r="X46" s="25"/>
+      <c r="Q46" s="21"/>
+      <c r="R46" s="20"/>
+      <c r="S46" s="21"/>
+      <c r="T46" s="20"/>
+      <c r="U46" s="20"/>
+      <c r="V46" s="21"/>
+      <c r="W46" s="22"/>
+      <c r="X46" s="48"/>
       <c r="Y46" s="8"/>
     </row>
     <row r="47" spans="1:25" ht="39.65" customHeight="1" thickBot="1">
-      <c r="A47" s="26" t="s">
+      <c r="A47" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="27"/>
-      <c r="K47" s="27"/>
-      <c r="L47" s="27"/>
-      <c r="M47" s="27"/>
-      <c r="N47" s="27"/>
-      <c r="O47" s="27"/>
-      <c r="P47" s="27"/>
-      <c r="Q47" s="27"/>
-      <c r="R47" s="27"/>
-      <c r="S47" s="27"/>
-      <c r="T47" s="27"/>
-      <c r="U47" s="27"/>
-      <c r="V47" s="27"/>
-      <c r="W47" s="27"/>
-      <c r="X47" s="28"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
+      <c r="G47" s="33"/>
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="33"/>
+      <c r="N47" s="33"/>
+      <c r="O47" s="33"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="33"/>
+      <c r="R47" s="33"/>
+      <c r="S47" s="33"/>
+      <c r="T47" s="33"/>
+      <c r="U47" s="33"/>
+      <c r="V47" s="33"/>
+      <c r="W47" s="33"/>
+      <c r="X47" s="34"/>
       <c r="Y47" s="9"/>
     </row>
     <row r="48" spans="1:25" ht="248" customHeight="1" thickBot="1">
-      <c r="A48" s="44" t="s">
+      <c r="A48" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="45"/>
-      <c r="M48" s="45"/>
-      <c r="N48" s="45"/>
-      <c r="O48" s="45"/>
-      <c r="P48" s="45"/>
-      <c r="Q48" s="45"/>
-      <c r="R48" s="45"/>
-      <c r="S48" s="45"/>
-      <c r="T48" s="45"/>
-      <c r="U48" s="45"/>
-      <c r="V48" s="45"/>
-      <c r="W48" s="45"/>
-      <c r="X48" s="46"/>
+      <c r="B48" s="50"/>
+      <c r="C48" s="50"/>
+      <c r="D48" s="50"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="50"/>
+      <c r="G48" s="50"/>
+      <c r="H48" s="50"/>
+      <c r="I48" s="50"/>
+      <c r="J48" s="50"/>
+      <c r="K48" s="50"/>
+      <c r="L48" s="50"/>
+      <c r="M48" s="50"/>
+      <c r="N48" s="50"/>
+      <c r="O48" s="50"/>
+      <c r="P48" s="50"/>
+      <c r="Q48" s="50"/>
+      <c r="R48" s="50"/>
+      <c r="S48" s="50"/>
+      <c r="T48" s="50"/>
+      <c r="U48" s="50"/>
+      <c r="V48" s="50"/>
+      <c r="W48" s="50"/>
+      <c r="X48" s="51"/>
       <c r="Y48" s="3"/>
     </row>
-    <row r="49" spans="1:25" ht="33" customHeight="1" thickTop="1">
+    <row r="49" spans="1:25" ht="33" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="3"/>
       <c r="C49" s="9"/>

--- a/templates/invigilation-template.xlsx
+++ b/templates/invigilation-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\school-substitution-sys\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF02F03F-3DD3-4FEF-B19A-683AFA70A135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD56792-04D2-4F52-9EEC-35D598CB4400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2D53BEDC-658E-4916-BAED-16A4B4875AEA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D53BEDC-658E-4916-BAED-16A4B4875AEA}"/>
   </bookViews>
   <sheets>
     <sheet name="114-1-1" sheetId="1" r:id="rId1"/>
@@ -83,15 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>備註:
-(1)請監考老師留意各科考試時間及節次，提早至教務處領取試卷，至少提前3分鐘入班，指導學生安靜入座，鐘響前發放完畢答案卡，鐘聲響起立即發下考卷，讓學生有完整時間作答。(一致性原則詳見段考範圍表所列注意事項)
-(2)各科考試時間皆為一節課(45分鐘)，測驗開始及結束時間皆以學校鐘聲為準。
-(3)監考表原則採隨班監考方式安排呈現，部分節次因命題巡堂與考科當節迴避而適度調整，請留意監考節次與班級。 
-(4)請老師專心監考，不要讓學生有作弊的機會，並請於非考試節次依本表準時入班監看自習。
-(5)校外教學期間，教師未執行課務(安排已劃底線註記)，依比例安排於本學年段考監考、監看自習或代理遺留課程【未執行的課務共_____節，本次段考已安排_____節，尚有____節，未執行節數將會累計於本學年度】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>08:30</t>
   </si>
   <si>
@@ -146,6 +137,15 @@
   </si>
   <si>
     <t>日  期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註:
+(1)請監考老師留意各科考試時間及節次，提早至教務處領取試卷，至少提前3分鐘入班，指導學生安靜入座，鐘響前發放完畢答案卡，鐘聲響起立即發下考卷，讓學生有完整時間作答。(一致性原則詳見段考範圍表所列注意事項)
+(2)各科考試時間皆為一節課(45分鐘)，測驗開始及結束時間皆以學校鐘聲為準。
+(3)監考表原則採隨班監考方式安排呈現，部分節次因命題巡堂與考科當節迴避而適度調整，請留意監考節次與班級。 
+(4)請老師專心監考，不要讓學生有作弊的機會，並請於非考試節次依本表準時入班監看自習。
+(5)校外教學期間，教師未執行課務(安排已劃底線註記)，依節次安排於本學年段考監考、監看自習或代理遺留課程【未執行的課務共_____節，本次段考已安排_____節，尚有____節，未執行節數將會累計於本學年度】</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -633,25 +633,9 @@
     <xf numFmtId="49" fontId="9" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -670,11 +654,27 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -898,84 +898,84 @@
   <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.25" style="12" customWidth="1"/>
-    <col min="2" max="12" width="7.08203125" customWidth="1"/>
-    <col min="13" max="13" width="9.1640625" customWidth="1"/>
-    <col min="14" max="22" width="7.08203125" customWidth="1"/>
-    <col min="23" max="23" width="7.08203125" style="13" customWidth="1"/>
-    <col min="24" max="24" width="7.08203125" customWidth="1"/>
-    <col min="25" max="25" width="6.83203125" customWidth="1"/>
+    <col min="2" max="12" width="7.125" customWidth="1"/>
+    <col min="13" max="13" width="9.125" customWidth="1"/>
+    <col min="14" max="22" width="7.125" customWidth="1"/>
+    <col min="23" max="23" width="7.125" style="13" customWidth="1"/>
+    <col min="24" max="24" width="7.125" customWidth="1"/>
+    <col min="25" max="25" width="6.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="2" customFormat="1" ht="43.5" customHeight="1" thickTop="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="40"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="47"/>
       <c r="Y1" s="1"/>
     </row>
     <row r="2" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="35" t="s">
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="37"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="50"/>
       <c r="M2" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
-      <c r="N2" s="35" t="s">
+      <c r="N2" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="35" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="42"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="51"/>
       <c r="Y2" s="3"/>
     </row>
     <row r="3" spans="1:25" ht="27.75" customHeight="1">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="15">
@@ -1012,7 +1012,7 @@
         <v>4</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N3" s="15">
         <v>1</v>
@@ -1044,328 +1044,328 @@
       <c r="W3" s="18">
         <v>3</v>
       </c>
-      <c r="X3" s="43">
+      <c r="X3" s="33">
         <v>4</v>
       </c>
       <c r="Y3" s="4"/>
     </row>
     <row r="4" spans="1:25" ht="27.75" customHeight="1">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="32" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="16"/>
       <c r="D4" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="17"/>
       <c r="F4" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J4" s="16"/>
       <c r="K4" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L4" s="17"/>
       <c r="M4" s="14" t="s">
         <v>2</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O4" s="16"/>
       <c r="P4" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q4" s="17"/>
       <c r="R4" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S4" s="16"/>
       <c r="T4" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U4" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V4" s="16"/>
       <c r="W4" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
-      <c r="X4" s="44"/>
+      <c r="X4" s="34"/>
       <c r="Y4" s="4"/>
     </row>
     <row r="5" spans="1:25" ht="27.75" customHeight="1">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="32" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L5" s="17"/>
       <c r="M5" s="14" t="s">
         <v>3</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S5" s="16"/>
       <c r="T5" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U5" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V5" s="17"/>
       <c r="W5" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
-      <c r="X5" s="44"/>
+      <c r="X5" s="34"/>
       <c r="Y5" s="4"/>
     </row>
     <row r="6" spans="1:25" ht="27.75" customHeight="1">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="32" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="17"/>
       <c r="F6" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L6" s="17"/>
       <c r="M6" s="14" t="s">
         <v>4</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O6" s="16"/>
       <c r="P6" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q6" s="17"/>
       <c r="R6" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S6" s="16"/>
       <c r="T6" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U6" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V6" s="17"/>
       <c r="W6" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
-      <c r="X6" s="44"/>
+      <c r="X6" s="34"/>
       <c r="Y6" s="4"/>
     </row>
     <row r="7" spans="1:25" ht="33" customHeight="1">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="32" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="D7" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="E7" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="F7" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="G7" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="H7" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="27" t="s">
-        <v>18</v>
+      <c r="I7" s="24" t="s">
+        <v>11</v>
       </c>
-      <c r="I7" s="24" t="s">
+      <c r="J7" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="K7" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="28" t="s">
+      <c r="L7" s="29" t="s">
         <v>14</v>
-      </c>
-      <c r="L7" s="29" t="s">
-        <v>15</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>5</v>
       </c>
       <c r="N7" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="O7" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="P7" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="P7" s="24" t="s">
+      <c r="Q7" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="Q7" s="26" t="s">
+      <c r="R7" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="R7" s="27" t="s">
+      <c r="S7" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S7" s="25" t="s">
+      <c r="T7" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="T7" s="27" t="s">
-        <v>18</v>
+      <c r="U7" s="24" t="s">
+        <v>11</v>
       </c>
-      <c r="U7" s="24" t="s">
+      <c r="V7" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="V7" s="25" t="s">
+      <c r="W7" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="W7" s="28" t="s">
+      <c r="X7" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="X7" s="45" t="s">
-        <v>15</v>
-      </c>
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="1:25" ht="30.75" customHeight="1">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="32" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="D8" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="E8" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="F8" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="G8" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="H8" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="27" t="s">
-        <v>25</v>
+      <c r="I8" s="27" t="s">
+        <v>18</v>
       </c>
-      <c r="I8" s="27" t="s">
+      <c r="J8" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="K8" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="K8" s="30" t="s">
+      <c r="L8" s="31" t="s">
         <v>21</v>
-      </c>
-      <c r="L8" s="31" t="s">
-        <v>22</v>
       </c>
       <c r="M8" s="19" t="s">
         <v>6</v>
       </c>
       <c r="N8" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="O8" s="25" t="s">
+      <c r="P8" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="27" t="s">
+      <c r="Q8" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="25" t="s">
+      <c r="R8" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="27" t="s">
+      <c r="S8" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="S8" s="25" t="s">
+      <c r="T8" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="T8" s="27" t="s">
-        <v>25</v>
+      <c r="U8" s="27" t="s">
+        <v>18</v>
       </c>
-      <c r="U8" s="27" t="s">
+      <c r="V8" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="V8" s="25" t="s">
+      <c r="W8" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="W8" s="30" t="s">
+      <c r="X8" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="X8" s="46" t="s">
-        <v>22</v>
-      </c>
       <c r="Y8" s="5"/>
     </row>
-    <row r="9" spans="1:25" ht="27.65" customHeight="1">
-      <c r="A9" s="47"/>
+    <row r="9" spans="1:25" ht="27.6" customHeight="1">
+      <c r="A9" s="37"/>
       <c r="B9" s="20"/>
       <c r="C9" s="21"/>
       <c r="D9" s="7"/>
@@ -1388,11 +1388,11 @@
       <c r="U9" s="20"/>
       <c r="V9" s="21"/>
       <c r="W9" s="22"/>
-      <c r="X9" s="48"/>
+      <c r="X9" s="38"/>
       <c r="Y9" s="8"/>
     </row>
-    <row r="10" spans="1:25" ht="30.65" customHeight="1">
-      <c r="A10" s="47"/>
+    <row r="10" spans="1:25" ht="30.6" customHeight="1">
+      <c r="A10" s="37"/>
       <c r="B10" s="20"/>
       <c r="C10" s="21"/>
       <c r="D10" s="7"/>
@@ -1415,11 +1415,11 @@
       <c r="U10" s="20"/>
       <c r="V10" s="21"/>
       <c r="W10" s="22"/>
-      <c r="X10" s="48"/>
+      <c r="X10" s="38"/>
       <c r="Y10" s="8"/>
     </row>
     <row r="11" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A11" s="47"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="20"/>
       <c r="C11" s="21"/>
       <c r="D11" s="7"/>
@@ -1442,11 +1442,11 @@
       <c r="U11" s="20"/>
       <c r="V11" s="21"/>
       <c r="W11" s="22"/>
-      <c r="X11" s="48"/>
+      <c r="X11" s="38"/>
       <c r="Y11" s="8"/>
     </row>
     <row r="12" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A12" s="47"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="20"/>
       <c r="C12" s="21"/>
       <c r="D12" s="7"/>
@@ -1469,11 +1469,11 @@
       <c r="U12" s="20"/>
       <c r="V12" s="21"/>
       <c r="W12" s="22"/>
-      <c r="X12" s="48"/>
+      <c r="X12" s="38"/>
       <c r="Y12" s="8"/>
     </row>
     <row r="13" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A13" s="47"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="20"/>
       <c r="C13" s="21"/>
       <c r="D13" s="7"/>
@@ -1496,11 +1496,11 @@
       <c r="U13" s="20"/>
       <c r="V13" s="21"/>
       <c r="W13" s="22"/>
-      <c r="X13" s="48"/>
+      <c r="X13" s="38"/>
       <c r="Y13" s="8"/>
     </row>
     <row r="14" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A14" s="47"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="20"/>
       <c r="C14" s="21"/>
       <c r="D14" s="7"/>
@@ -1523,11 +1523,11 @@
       <c r="U14" s="20"/>
       <c r="V14" s="21"/>
       <c r="W14" s="22"/>
-      <c r="X14" s="48"/>
+      <c r="X14" s="38"/>
       <c r="Y14" s="8"/>
     </row>
     <row r="15" spans="1:25" ht="30.75" customHeight="1">
-      <c r="A15" s="47"/>
+      <c r="A15" s="37"/>
       <c r="B15" s="20"/>
       <c r="C15" s="21"/>
       <c r="D15" s="7"/>
@@ -1550,11 +1550,11 @@
       <c r="U15" s="20"/>
       <c r="V15" s="21"/>
       <c r="W15" s="22"/>
-      <c r="X15" s="48"/>
+      <c r="X15" s="38"/>
       <c r="Y15" s="8"/>
     </row>
     <row r="16" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A16" s="47"/>
+      <c r="A16" s="37"/>
       <c r="B16" s="20"/>
       <c r="C16" s="21"/>
       <c r="D16" s="7"/>
@@ -1577,11 +1577,11 @@
       <c r="U16" s="20"/>
       <c r="V16" s="21"/>
       <c r="W16" s="22"/>
-      <c r="X16" s="48"/>
+      <c r="X16" s="38"/>
       <c r="Y16" s="8"/>
     </row>
     <row r="17" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A17" s="47"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="20"/>
       <c r="C17" s="21"/>
       <c r="D17" s="7"/>
@@ -1604,11 +1604,11 @@
       <c r="U17" s="20"/>
       <c r="V17" s="21"/>
       <c r="W17" s="22"/>
-      <c r="X17" s="48"/>
+      <c r="X17" s="38"/>
       <c r="Y17" s="8"/>
     </row>
     <row r="18" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A18" s="47"/>
+      <c r="A18" s="37"/>
       <c r="B18" s="20"/>
       <c r="C18" s="21"/>
       <c r="D18" s="7"/>
@@ -1631,11 +1631,11 @@
       <c r="U18" s="20"/>
       <c r="V18" s="21"/>
       <c r="W18" s="22"/>
-      <c r="X18" s="48"/>
+      <c r="X18" s="38"/>
       <c r="Y18" s="8"/>
     </row>
     <row r="19" spans="1:25" ht="27.75" customHeight="1">
-      <c r="A19" s="47"/>
+      <c r="A19" s="37"/>
       <c r="B19" s="20"/>
       <c r="C19" s="21"/>
       <c r="D19" s="7"/>
@@ -1658,11 +1658,11 @@
       <c r="U19" s="20"/>
       <c r="V19" s="21"/>
       <c r="W19" s="22"/>
-      <c r="X19" s="48"/>
+      <c r="X19" s="38"/>
       <c r="Y19" s="8"/>
     </row>
     <row r="20" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A20" s="47"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="20"/>
       <c r="C20" s="21"/>
       <c r="D20" s="7"/>
@@ -1685,11 +1685,11 @@
       <c r="U20" s="20"/>
       <c r="V20" s="21"/>
       <c r="W20" s="22"/>
-      <c r="X20" s="48"/>
+      <c r="X20" s="38"/>
       <c r="Y20" s="8"/>
     </row>
     <row r="21" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A21" s="47"/>
+      <c r="A21" s="37"/>
       <c r="B21" s="20"/>
       <c r="C21" s="21"/>
       <c r="D21" s="7"/>
@@ -1712,11 +1712,11 @@
       <c r="U21" s="20"/>
       <c r="V21" s="21"/>
       <c r="W21" s="22"/>
-      <c r="X21" s="48"/>
+      <c r="X21" s="38"/>
       <c r="Y21" s="8"/>
     </row>
     <row r="22" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A22" s="47"/>
+      <c r="A22" s="37"/>
       <c r="B22" s="20"/>
       <c r="C22" s="21"/>
       <c r="D22" s="7"/>
@@ -1739,11 +1739,11 @@
       <c r="U22" s="20"/>
       <c r="V22" s="21"/>
       <c r="W22" s="22"/>
-      <c r="X22" s="48"/>
+      <c r="X22" s="38"/>
       <c r="Y22" s="8"/>
     </row>
     <row r="23" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A23" s="47"/>
+      <c r="A23" s="37"/>
       <c r="B23" s="20"/>
       <c r="C23" s="21"/>
       <c r="D23" s="7"/>
@@ -1766,11 +1766,11 @@
       <c r="U23" s="20"/>
       <c r="V23" s="21"/>
       <c r="W23" s="22"/>
-      <c r="X23" s="48"/>
+      <c r="X23" s="38"/>
       <c r="Y23" s="8"/>
     </row>
     <row r="24" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A24" s="47"/>
+      <c r="A24" s="37"/>
       <c r="B24" s="20"/>
       <c r="C24" s="21"/>
       <c r="D24" s="7"/>
@@ -1793,11 +1793,11 @@
       <c r="U24" s="20"/>
       <c r="V24" s="21"/>
       <c r="W24" s="22"/>
-      <c r="X24" s="48"/>
+      <c r="X24" s="38"/>
       <c r="Y24" s="8"/>
     </row>
     <row r="25" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A25" s="47"/>
+      <c r="A25" s="37"/>
       <c r="B25" s="20"/>
       <c r="C25" s="21"/>
       <c r="D25" s="7"/>
@@ -1820,11 +1820,11 @@
       <c r="U25" s="20"/>
       <c r="V25" s="21"/>
       <c r="W25" s="22"/>
-      <c r="X25" s="48"/>
+      <c r="X25" s="38"/>
       <c r="Y25" s="8"/>
     </row>
     <row r="26" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A26" s="47"/>
+      <c r="A26" s="37"/>
       <c r="B26" s="20"/>
       <c r="C26" s="21"/>
       <c r="D26" s="7"/>
@@ -1847,11 +1847,11 @@
       <c r="U26" s="20"/>
       <c r="V26" s="21"/>
       <c r="W26" s="22"/>
-      <c r="X26" s="48"/>
+      <c r="X26" s="38"/>
       <c r="Y26" s="8"/>
     </row>
     <row r="27" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A27" s="47"/>
+      <c r="A27" s="37"/>
       <c r="B27" s="20"/>
       <c r="C27" s="21"/>
       <c r="D27" s="7"/>
@@ -1874,11 +1874,11 @@
       <c r="U27" s="20"/>
       <c r="V27" s="21"/>
       <c r="W27" s="22"/>
-      <c r="X27" s="48"/>
+      <c r="X27" s="38"/>
       <c r="Y27" s="8"/>
     </row>
     <row r="28" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A28" s="47"/>
+      <c r="A28" s="37"/>
       <c r="B28" s="20"/>
       <c r="C28" s="21"/>
       <c r="D28" s="7"/>
@@ -1901,11 +1901,11 @@
       <c r="U28" s="20"/>
       <c r="V28" s="21"/>
       <c r="W28" s="22"/>
-      <c r="X28" s="48"/>
+      <c r="X28" s="38"/>
       <c r="Y28" s="8"/>
     </row>
     <row r="29" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A29" s="47"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="20"/>
       <c r="C29" s="21"/>
       <c r="D29" s="7"/>
@@ -1928,11 +1928,11 @@
       <c r="U29" s="20"/>
       <c r="V29" s="21"/>
       <c r="W29" s="22"/>
-      <c r="X29" s="48"/>
+      <c r="X29" s="38"/>
       <c r="Y29" s="8"/>
     </row>
     <row r="30" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A30" s="47"/>
+      <c r="A30" s="37"/>
       <c r="B30" s="20"/>
       <c r="C30" s="21"/>
       <c r="D30" s="7"/>
@@ -1955,11 +1955,11 @@
       <c r="U30" s="20"/>
       <c r="V30" s="21"/>
       <c r="W30" s="22"/>
-      <c r="X30" s="48"/>
+      <c r="X30" s="38"/>
       <c r="Y30" s="8"/>
     </row>
     <row r="31" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A31" s="47"/>
+      <c r="A31" s="37"/>
       <c r="B31" s="20"/>
       <c r="C31" s="21"/>
       <c r="D31" s="7"/>
@@ -1982,11 +1982,11 @@
       <c r="U31" s="20"/>
       <c r="V31" s="21"/>
       <c r="W31" s="22"/>
-      <c r="X31" s="48"/>
+      <c r="X31" s="38"/>
       <c r="Y31" s="8"/>
     </row>
     <row r="32" spans="1:25" ht="30" customHeight="1">
-      <c r="A32" s="47"/>
+      <c r="A32" s="37"/>
       <c r="B32" s="20"/>
       <c r="C32" s="21"/>
       <c r="D32" s="7"/>
@@ -2009,11 +2009,11 @@
       <c r="U32" s="20"/>
       <c r="V32" s="21"/>
       <c r="W32" s="22"/>
-      <c r="X32" s="48"/>
+      <c r="X32" s="38"/>
       <c r="Y32" s="8"/>
     </row>
     <row r="33" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A33" s="47"/>
+      <c r="A33" s="37"/>
       <c r="B33" s="20"/>
       <c r="C33" s="21"/>
       <c r="D33" s="7"/>
@@ -2036,11 +2036,11 @@
       <c r="U33" s="20"/>
       <c r="V33" s="21"/>
       <c r="W33" s="22"/>
-      <c r="X33" s="48"/>
+      <c r="X33" s="38"/>
       <c r="Y33" s="8"/>
     </row>
     <row r="34" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A34" s="47"/>
+      <c r="A34" s="37"/>
       <c r="B34" s="20"/>
       <c r="C34" s="21"/>
       <c r="D34" s="7"/>
@@ -2063,11 +2063,11 @@
       <c r="U34" s="20"/>
       <c r="V34" s="21"/>
       <c r="W34" s="22"/>
-      <c r="X34" s="48"/>
+      <c r="X34" s="38"/>
       <c r="Y34" s="8"/>
     </row>
     <row r="35" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A35" s="47"/>
+      <c r="A35" s="37"/>
       <c r="B35" s="20"/>
       <c r="C35" s="21"/>
       <c r="D35" s="7"/>
@@ -2090,11 +2090,11 @@
       <c r="U35" s="20"/>
       <c r="V35" s="21"/>
       <c r="W35" s="22"/>
-      <c r="X35" s="48"/>
+      <c r="X35" s="38"/>
       <c r="Y35" s="8"/>
     </row>
     <row r="36" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A36" s="47"/>
+      <c r="A36" s="37"/>
       <c r="B36" s="20"/>
       <c r="C36" s="21"/>
       <c r="D36" s="7"/>
@@ -2117,11 +2117,11 @@
       <c r="U36" s="20"/>
       <c r="V36" s="21"/>
       <c r="W36" s="22"/>
-      <c r="X36" s="48"/>
+      <c r="X36" s="38"/>
       <c r="Y36" s="8"/>
     </row>
     <row r="37" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A37" s="47"/>
+      <c r="A37" s="37"/>
       <c r="B37" s="20"/>
       <c r="C37" s="21"/>
       <c r="D37" s="7"/>
@@ -2144,11 +2144,11 @@
       <c r="U37" s="20"/>
       <c r="V37" s="21"/>
       <c r="W37" s="22"/>
-      <c r="X37" s="48"/>
+      <c r="X37" s="38"/>
       <c r="Y37" s="8"/>
     </row>
     <row r="38" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A38" s="47"/>
+      <c r="A38" s="37"/>
       <c r="B38" s="20"/>
       <c r="C38" s="21"/>
       <c r="D38" s="7"/>
@@ -2171,11 +2171,11 @@
       <c r="U38" s="20"/>
       <c r="V38" s="21"/>
       <c r="W38" s="22"/>
-      <c r="X38" s="48"/>
+      <c r="X38" s="38"/>
       <c r="Y38" s="8"/>
     </row>
     <row r="39" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A39" s="47"/>
+      <c r="A39" s="37"/>
       <c r="B39" s="20"/>
       <c r="C39" s="21"/>
       <c r="D39" s="7"/>
@@ -2198,11 +2198,11 @@
       <c r="U39" s="20"/>
       <c r="V39" s="21"/>
       <c r="W39" s="22"/>
-      <c r="X39" s="48"/>
+      <c r="X39" s="38"/>
       <c r="Y39" s="8"/>
     </row>
     <row r="40" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A40" s="47"/>
+      <c r="A40" s="37"/>
       <c r="B40" s="20"/>
       <c r="C40" s="21"/>
       <c r="D40" s="7"/>
@@ -2225,11 +2225,11 @@
       <c r="U40" s="20"/>
       <c r="V40" s="21"/>
       <c r="W40" s="22"/>
-      <c r="X40" s="48"/>
+      <c r="X40" s="38"/>
       <c r="Y40" s="8"/>
     </row>
     <row r="41" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A41" s="47"/>
+      <c r="A41" s="37"/>
       <c r="B41" s="20"/>
       <c r="C41" s="21"/>
       <c r="D41" s="7"/>
@@ -2252,11 +2252,11 @@
       <c r="U41" s="20"/>
       <c r="V41" s="21"/>
       <c r="W41" s="22"/>
-      <c r="X41" s="48"/>
+      <c r="X41" s="38"/>
       <c r="Y41" s="8"/>
     </row>
     <row r="42" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A42" s="47"/>
+      <c r="A42" s="37"/>
       <c r="B42" s="20"/>
       <c r="C42" s="21"/>
       <c r="D42" s="7"/>
@@ -2279,11 +2279,11 @@
       <c r="U42" s="20"/>
       <c r="V42" s="21"/>
       <c r="W42" s="22"/>
-      <c r="X42" s="48"/>
+      <c r="X42" s="38"/>
       <c r="Y42" s="8"/>
     </row>
     <row r="43" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A43" s="47"/>
+      <c r="A43" s="37"/>
       <c r="B43" s="20"/>
       <c r="C43" s="21"/>
       <c r="D43" s="7"/>
@@ -2306,11 +2306,11 @@
       <c r="U43" s="20"/>
       <c r="V43" s="21"/>
       <c r="W43" s="22"/>
-      <c r="X43" s="48"/>
+      <c r="X43" s="38"/>
       <c r="Y43" s="8"/>
     </row>
     <row r="44" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A44" s="47"/>
+      <c r="A44" s="37"/>
       <c r="B44" s="20"/>
       <c r="C44" s="21"/>
       <c r="D44" s="7"/>
@@ -2333,11 +2333,11 @@
       <c r="U44" s="20"/>
       <c r="V44" s="21"/>
       <c r="W44" s="22"/>
-      <c r="X44" s="48"/>
+      <c r="X44" s="38"/>
       <c r="Y44" s="8"/>
     </row>
     <row r="45" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A45" s="47"/>
+      <c r="A45" s="37"/>
       <c r="B45" s="20"/>
       <c r="C45" s="21"/>
       <c r="D45" s="7"/>
@@ -2360,11 +2360,11 @@
       <c r="U45" s="20"/>
       <c r="V45" s="21"/>
       <c r="W45" s="22"/>
-      <c r="X45" s="48"/>
+      <c r="X45" s="38"/>
       <c r="Y45" s="8"/>
     </row>
     <row r="46" spans="1:25" ht="28.5" customHeight="1" thickBot="1">
-      <c r="A46" s="47"/>
+      <c r="A46" s="37"/>
       <c r="B46" s="20"/>
       <c r="C46" s="21"/>
       <c r="D46" s="7"/>
@@ -2387,65 +2387,65 @@
       <c r="U46" s="20"/>
       <c r="V46" s="21"/>
       <c r="W46" s="22"/>
-      <c r="X46" s="48"/>
+      <c r="X46" s="38"/>
       <c r="Y46" s="8"/>
     </row>
-    <row r="47" spans="1:25" ht="39.65" customHeight="1" thickBot="1">
-      <c r="A47" s="32" t="s">
+    <row r="47" spans="1:25" ht="39.6" customHeight="1" thickBot="1">
+      <c r="A47" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="33"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="33"/>
-      <c r="M47" s="33"/>
-      <c r="N47" s="33"/>
-      <c r="O47" s="33"/>
-      <c r="P47" s="33"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="33"/>
-      <c r="S47" s="33"/>
-      <c r="T47" s="33"/>
-      <c r="U47" s="33"/>
-      <c r="V47" s="33"/>
-      <c r="W47" s="33"/>
-      <c r="X47" s="34"/>
+      <c r="B47" s="40"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="40"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="40"/>
+      <c r="J47" s="40"/>
+      <c r="K47" s="40"/>
+      <c r="L47" s="40"/>
+      <c r="M47" s="40"/>
+      <c r="N47" s="40"/>
+      <c r="O47" s="40"/>
+      <c r="P47" s="40"/>
+      <c r="Q47" s="40"/>
+      <c r="R47" s="40"/>
+      <c r="S47" s="40"/>
+      <c r="T47" s="40"/>
+      <c r="U47" s="40"/>
+      <c r="V47" s="40"/>
+      <c r="W47" s="40"/>
+      <c r="X47" s="41"/>
       <c r="Y47" s="9"/>
     </row>
-    <row r="48" spans="1:25" ht="248" customHeight="1" thickBot="1">
-      <c r="A48" s="49" t="s">
-        <v>11</v>
+    <row r="48" spans="1:25" ht="248.1" customHeight="1" thickBot="1">
+      <c r="A48" s="42" t="s">
+        <v>29</v>
       </c>
-      <c r="B48" s="50"/>
-      <c r="C48" s="50"/>
-      <c r="D48" s="50"/>
-      <c r="E48" s="50"/>
-      <c r="F48" s="50"/>
-      <c r="G48" s="50"/>
-      <c r="H48" s="50"/>
-      <c r="I48" s="50"/>
-      <c r="J48" s="50"/>
-      <c r="K48" s="50"/>
-      <c r="L48" s="50"/>
-      <c r="M48" s="50"/>
-      <c r="N48" s="50"/>
-      <c r="O48" s="50"/>
-      <c r="P48" s="50"/>
-      <c r="Q48" s="50"/>
-      <c r="R48" s="50"/>
-      <c r="S48" s="50"/>
-      <c r="T48" s="50"/>
-      <c r="U48" s="50"/>
-      <c r="V48" s="50"/>
-      <c r="W48" s="50"/>
-      <c r="X48" s="51"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+      <c r="L48" s="43"/>
+      <c r="M48" s="43"/>
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="43"/>
+      <c r="T48" s="43"/>
+      <c r="U48" s="43"/>
+      <c r="V48" s="43"/>
+      <c r="W48" s="43"/>
+      <c r="X48" s="44"/>
       <c r="Y48" s="3"/>
     </row>
     <row r="49" spans="1:25" ht="33" customHeight="1">
@@ -28273,7 +28273,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.19685039370078741" top="0.35433070866141736" bottom="0.35433070866141736" header="0" footer="0"/>
-  <pageSetup paperSize="12" scale="60" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="12" scale="61" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="48" max="16383" man="1"/>
     <brk id="49" max="16383" man="1"/>
